--- a/tests/fixtures/FM_SYNTHETIQUE_REF.xlsx
+++ b/tests/fixtures/FM_SYNTHETIQUE_REF.xlsx
@@ -7609,7 +7609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8560,57 +8560,78 @@
     <row r="64">
       <c r="B64" s="8" t="inlineStr">
         <is>
+          <t>Charges à répartir sur plusieurs exercices</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="8" t="inlineStr">
+        <is>
           <t>Charges constatées d'avance</t>
         </is>
       </c>
-      <c r="D64" s="9" t="n">
+      <c r="D65" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="E64" s="9" t="n">
+      <c r="E65" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="F64" s="9" t="n">
+      <c r="F65" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G64" s="10" t="n">
+      <c r="G65" s="10" t="n">
         <v>0.5455</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="12" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>Comptes de régularisation</t>
         </is>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D66" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="E65" s="13" t="n">
+      <c r="E66" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="F65" s="13" t="n">
+      <c r="F66" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="G65" s="14" t="n">
+      <c r="G66" s="14" t="n">
         <v>0.5455</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="12" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>TOTAL ACTIF</t>
         </is>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D68" s="13" t="n">
         <v>1293.9</v>
       </c>
-      <c r="E67" s="13" t="n">
+      <c r="E68" s="13" t="n">
         <v>676.8</v>
       </c>
-      <c r="F67" s="13" t="n">
+      <c r="F68" s="13" t="n">
         <v>617.1</v>
       </c>
-      <c r="G67" s="14" t="n">
+      <c r="G68" s="14" t="n">
         <v>0.9118000000000001</v>
       </c>
     </row>
